--- a/checkrates/week-19/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-19/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -847,14 +847,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B2B Opaco · BKGS&gt;0 · peor Eficacia · ordenado ↑</t>
+          <t>B2B Opaco · BKGS&gt;0 · peor Eficacia · ordenado por Eficacia ↑ (menor primero)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -7574,18 +7574,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7605,7 +7606,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -7622,35 +7623,40 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>Channels</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Successful</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>BandaEficacia</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaConvRate</t>
         </is>
@@ -7665,27 +7671,32 @@
           <t>IHG</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Expedia, Internal</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
         <v>379911</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="E6" s="12" t="n">
         <v>349010</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="F6" s="12" t="n">
         <v>5285</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="G6" s="13" t="n">
         <v>0.9186625288554424</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="H6" s="13" t="n">
         <v>0.01391115287527868</v>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -7700,27 +7711,32 @@
           <t>Hilton</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, HBSI, Internal</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
         <v>255301</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="E7" s="12" t="n">
         <v>247329</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>2493</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="G7" s="13" t="n">
         <v>0.9687741136932484</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="H7" s="13" t="n">
         <v>0.009764944124778203</v>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -7735,27 +7751,32 @@
           <t>Hyatt</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
         <v>157813</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="E8" s="12" t="n">
         <v>152843</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>1822</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="G8" s="13" t="n">
         <v>0.9685070304727748</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="H8" s="13" t="n">
         <v>0.01154530995545361</v>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -7770,27 +7791,32 @@
           <t>Accor</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Expedia, HotelBeds Apitude, Internal</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
         <v>39908</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="E9" s="12" t="n">
         <v>37392</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="G9" s="13" t="n">
         <v>0.9369549964919315</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="H9" s="13" t="n">
         <v>0.001829207176505964</v>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7805,27 +7831,32 @@
           <t>AA-Independent</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, HBSI, HotelBeds Apitude, Internal, Siteminder, SynXis, Travelclick</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>34220</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="E10" s="12" t="n">
         <v>31588</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>693</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="G10" s="13" t="n">
         <v>0.9230859146697837</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="H10" s="13" t="n">
         <v>0.02025131502045588</v>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -7840,27 +7871,32 @@
           <t>Caesars Entertainment</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
         <v>24282</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="E11" s="12" t="n">
         <v>19575</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>203</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="G11" s="13" t="n">
         <v>0.8061527057079318</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.008360102133267442</v>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -7875,27 +7911,32 @@
           <t>Wyndham</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Internal, Siteminder</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
         <v>22743</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="E12" s="12" t="n">
         <v>21688</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="G12" s="13" t="n">
         <v>0.9536121004265049</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="H12" s="13" t="n">
         <v>0.004177109440267335</v>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7910,27 +7951,32 @@
           <t>Marriott</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Expedia, Internal</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
         <v>19778</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="E13" s="12" t="n">
         <v>19449</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="G13" s="13" t="n">
         <v>0.9833653554454445</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="H13" s="13" t="n">
         <v>0.001820204267367782</v>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7945,27 +7991,32 @@
           <t>MGM Resorts</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n">
         <v>17502</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="E14" s="12" t="n">
         <v>17218</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>235</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="G14" s="13" t="n">
         <v>0.9837732830533653</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="H14" s="13" t="n">
         <v>0.01342703691006742</v>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -7980,27 +8031,32 @@
           <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
         <v>11293</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="E15" s="12" t="n">
         <v>11222</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="G15" s="13" t="n">
         <v>0.9937129195076596</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="H15" s="13" t="n">
         <v>0.006287080492340388</v>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8015,27 +8071,32 @@
           <t>Barcelo</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>SynXis</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="n">
         <v>8008</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="E16" s="12" t="n">
         <v>7254</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="G16" s="13" t="n">
         <v>0.9058441558441559</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="H16" s="13" t="n">
         <v>0.009365634365634366</v>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -8050,27 +8111,32 @@
           <t>Disney</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
         <v>7255</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="E17" s="12" t="n">
         <v>7171</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="G17" s="13" t="n">
         <v>0.9884217780840799</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="H17" s="13" t="n">
         <v>0.004824259131633356</v>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8085,27 +8151,32 @@
           <t>Best Western</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Expedia, SynXis</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n">
         <v>6397</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="E18" s="12" t="n">
         <v>5927</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="G18" s="13" t="n">
         <v>0.9265280600281381</v>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="H18" s="13" t="n">
         <v>0.002970142254181648</v>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8120,27 +8191,32 @@
           <t>Palladium Hotel Group</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n">
-        <v>5352</v>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
       </c>
       <c r="D19" s="12" t="n">
         <v>5352</v>
       </c>
       <c r="E19" s="12" t="n">
+        <v>5352</v>
+      </c>
+      <c r="F19" s="12" t="n">
         <v>262</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="G19" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="H19" s="13" t="n">
         <v>0.04895366218236173</v>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8155,27 +8231,32 @@
           <t>Universal</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="n">
         <v>4725</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="E20" s="12" t="n">
         <v>3579</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F20" s="13" t="n">
+      <c r="G20" s="13" t="n">
         <v>0.7574603174603175</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="H20" s="13" t="n">
         <v>0.005291005291005291</v>
       </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8190,27 +8271,32 @@
           <t>PAM Hotels</t>
         </is>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Internal, SynXis</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="n">
         <v>4116</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="E21" s="12" t="n">
         <v>4046</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="G21" s="13" t="n">
         <v>0.9829931972789115</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="H21" s="13" t="n">
         <v>0.01676384839650146</v>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8225,27 +8311,32 @@
           <t>Hoteles Xcaret</t>
         </is>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="n">
         <v>4032</v>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="E22" s="12" t="n">
         <v>4020</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F22" s="13" t="n">
+      <c r="G22" s="13" t="n">
         <v>0.9970238095238095</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="H22" s="13" t="n">
         <v>0.003472222222222222</v>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8260,27 +8351,32 @@
           <t>Park Royal</t>
         </is>
       </c>
-      <c r="C23" s="12" t="n">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Internal</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="n">
         <v>3318</v>
       </c>
-      <c r="D23" s="12" t="n">
+      <c r="E23" s="12" t="n">
         <v>3282</v>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="G23" s="13" t="n">
         <v>0.9891500904159132</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="H23" s="13" t="n">
         <v>0.01868595539481615</v>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8295,27 +8391,32 @@
           <t>RIU</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n">
-        <v>2624</v>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D24" s="12" t="n">
         <v>2624</v>
       </c>
       <c r="E24" s="12" t="n">
+        <v>2624</v>
+      </c>
+      <c r="F24" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F24" s="13" t="n">
+      <c r="G24" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="H24" s="13" t="n">
         <v>0.01333841463414634</v>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -8330,27 +8431,32 @@
           <t>Decameron</t>
         </is>
       </c>
-      <c r="C25" s="12" t="n">
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n">
         <v>2570</v>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="E25" s="12" t="n">
         <v>2041</v>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="G25" s="13" t="n">
         <v>0.7941634241245136</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="H25" s="13" t="n">
         <v>0.04202334630350195</v>
       </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8365,27 +8471,32 @@
           <t>Ocean by H10</t>
         </is>
       </c>
-      <c r="C26" s="12" t="n">
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="n">
         <v>2298</v>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="E26" s="12" t="n">
         <v>2254</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="G26" s="13" t="n">
         <v>0.9808529155787642</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="H26" s="13" t="n">
         <v>0.01087902523933855</v>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -8400,27 +8511,32 @@
           <t>GRUPO POSADAS</t>
         </is>
       </c>
-      <c r="C27" s="12" t="n">
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="n">
         <v>2200</v>
       </c>
-      <c r="D27" s="12" t="n">
+      <c r="E27" s="12" t="n">
         <v>2128</v>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="G27" s="13" t="n">
         <v>0.9672727272727273</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="H27" s="13" t="n">
         <v>0.02318181818181818</v>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8435,27 +8551,32 @@
           <t>Emporio</t>
         </is>
       </c>
-      <c r="C28" s="12" t="n">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Internal, Siteminder</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="n">
         <v>2189</v>
       </c>
-      <c r="D28" s="12" t="n">
+      <c r="E28" s="12" t="n">
         <v>2167</v>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="F28" s="13" t="n">
+      <c r="G28" s="13" t="n">
         <v>0.9899497487437185</v>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="H28" s="13" t="n">
         <v>0.02329830973047053</v>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8470,27 +8591,32 @@
           <t>Presidente Intercontinental</t>
         </is>
       </c>
-      <c r="C29" s="12" t="n">
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Internal</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n">
         <v>2156</v>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="E29" s="12" t="n">
         <v>1913</v>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="F29" s="13" t="n">
+      <c r="G29" s="13" t="n">
         <v>0.887291280148423</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="H29" s="13" t="n">
         <v>0.02411873840445269</v>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8505,27 +8631,32 @@
           <t>Melia</t>
         </is>
       </c>
-      <c r="C30" s="12" t="n">
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="n">
         <v>1994</v>
       </c>
-      <c r="D30" s="12" t="n">
+      <c r="E30" s="12" t="n">
         <v>1146</v>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="G30" s="13" t="n">
         <v>0.5747241725175527</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="H30" s="13" t="n">
         <v>0.001504513540621865</v>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8540,27 +8671,32 @@
           <t>Krystal</t>
         </is>
       </c>
-      <c r="C31" s="12" t="n">
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="n">
         <v>1989</v>
       </c>
-      <c r="D31" s="12" t="n">
+      <c r="E31" s="12" t="n">
         <v>1959</v>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="G31" s="13" t="n">
         <v>0.9849170437405732</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="H31" s="13" t="n">
         <v>0.01508295625942685</v>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8575,27 +8711,32 @@
           <t>CHOICE</t>
         </is>
       </c>
-      <c r="C32" s="12" t="n">
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Expedia, Internal</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="n">
         <v>1781</v>
       </c>
-      <c r="D32" s="12" t="n">
+      <c r="E32" s="12" t="n">
         <v>1639</v>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F32" s="13" t="n">
+      <c r="G32" s="13" t="n">
         <v>0.9202695115103874</v>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="H32" s="13" t="n">
         <v>0.002245929253228523</v>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8610,27 +8751,32 @@
           <t>Palace</t>
         </is>
       </c>
-      <c r="C33" s="12" t="n">
-        <v>1484</v>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D33" s="12" t="n">
         <v>1484</v>
       </c>
       <c r="E33" s="12" t="n">
+        <v>1484</v>
+      </c>
+      <c r="F33" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="F33" s="13" t="n">
+      <c r="G33" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="H33" s="13" t="n">
         <v>0.02021563342318059</v>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8645,27 +8791,32 @@
           <t>Wynn Las Vegas</t>
         </is>
       </c>
-      <c r="C34" s="12" t="n">
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="n">
         <v>1365</v>
       </c>
-      <c r="D34" s="12" t="n">
+      <c r="E34" s="12" t="n">
         <v>1361</v>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F34" s="13" t="n">
+      <c r="G34" s="13" t="n">
         <v>0.9970695970695971</v>
       </c>
-      <c r="G34" s="13" t="n">
+      <c r="H34" s="13" t="n">
         <v>0.008791208791208791</v>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -8680,27 +8831,32 @@
           <t>Karisma</t>
         </is>
       </c>
-      <c r="C35" s="12" t="n">
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>SynXis</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="n">
         <v>1236</v>
       </c>
-      <c r="D35" s="12" t="n">
+      <c r="E35" s="12" t="n">
         <v>1165</v>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="F35" s="13" t="n">
+      <c r="G35" s="13" t="n">
         <v>0.9425566343042071</v>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="H35" s="13" t="n">
         <v>0.02184466019417476</v>
       </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8715,27 +8871,32 @@
           <t>Las Brisas</t>
         </is>
       </c>
-      <c r="C36" s="12" t="n">
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="n">
         <v>1210</v>
       </c>
-      <c r="D36" s="12" t="n">
+      <c r="E36" s="12" t="n">
         <v>1202</v>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="F36" s="13" t="n">
+      <c r="G36" s="13" t="n">
         <v>0.9933884297520661</v>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="H36" s="13" t="n">
         <v>0.04049586776859504</v>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8750,27 +8911,32 @@
           <t>Royalton Hotels &amp; Resorts</t>
         </is>
       </c>
-      <c r="C37" s="12" t="n">
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>SynXis</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="n">
         <v>1164</v>
       </c>
-      <c r="D37" s="12" t="n">
+      <c r="E37" s="12" t="n">
         <v>1102</v>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F37" s="13" t="n">
+      <c r="G37" s="13" t="n">
         <v>0.9467353951890034</v>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="H37" s="13" t="n">
         <v>0.003436426116838488</v>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8785,27 +8951,32 @@
           <t>Oasis</t>
         </is>
       </c>
-      <c r="C38" s="12" t="n">
-        <v>1067</v>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D38" s="12" t="n">
         <v>1067</v>
       </c>
       <c r="E38" s="12" t="n">
+        <v>1067</v>
+      </c>
+      <c r="F38" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F38" s="13" t="n">
+      <c r="G38" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="13" t="n">
+      <c r="H38" s="13" t="n">
         <v>0.00937207122774133</v>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -8820,27 +8991,32 @@
           <t>Bahia Principe</t>
         </is>
       </c>
-      <c r="C39" s="12" t="n">
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="n">
         <v>1003</v>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="E39" s="12" t="n">
         <v>985</v>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="F39" s="13" t="n">
+      <c r="G39" s="13" t="n">
         <v>0.9820538384845464</v>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="H39" s="13" t="n">
         <v>0.02392821535393819</v>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8855,27 +9031,32 @@
           <t>Camino Real</t>
         </is>
       </c>
-      <c r="C40" s="12" t="n">
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Internal, Travelclick</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="n">
         <v>901</v>
       </c>
-      <c r="D40" s="12" t="n">
+      <c r="E40" s="12" t="n">
         <v>899</v>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="F40" s="13" t="n">
+      <c r="G40" s="13" t="n">
         <v>0.9977802441731409</v>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="H40" s="13" t="n">
         <v>0.05438401775804662</v>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8890,27 +9071,32 @@
           <t>GHL</t>
         </is>
       </c>
-      <c r="C41" s="12" t="n">
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="n">
         <v>876</v>
       </c>
-      <c r="D41" s="12" t="n">
+      <c r="E41" s="12" t="n">
         <v>863</v>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="F41" s="13" t="n">
+      <c r="G41" s="13" t="n">
         <v>0.9851598173515982</v>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="H41" s="13" t="n">
         <v>0.02625570776255708</v>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8925,27 +9111,32 @@
           <t>Iberostar</t>
         </is>
       </c>
-      <c r="C42" s="12" t="n">
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="n">
         <v>781</v>
       </c>
-      <c r="D42" s="12" t="n">
+      <c r="E42" s="12" t="n">
         <v>405</v>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F42" s="13" t="n">
+      <c r="G42" s="13" t="n">
         <v>0.5185659411011524</v>
       </c>
-      <c r="G42" s="13" t="n">
+      <c r="H42" s="13" t="n">
         <v>0.001280409731113956</v>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="I42" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8960,27 +9151,32 @@
           <t>Hoteles Geh Suites</t>
         </is>
       </c>
-      <c r="C43" s="12" t="n">
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="n">
         <v>758</v>
       </c>
-      <c r="D43" s="12" t="n">
+      <c r="E43" s="12" t="n">
         <v>735</v>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="F43" s="13" t="n">
+      <c r="G43" s="13" t="n">
         <v>0.9696569920844327</v>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="H43" s="13" t="n">
         <v>0.01978891820580475</v>
       </c>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8995,27 +9191,32 @@
           <t>Dann</t>
         </is>
       </c>
-      <c r="C44" s="12" t="n">
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="n">
         <v>652</v>
       </c>
-      <c r="D44" s="12" t="n">
+      <c r="E44" s="12" t="n">
         <v>648</v>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="13" t="n">
+      <c r="G44" s="13" t="n">
         <v>0.9938650306748467</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="H44" s="13" t="n">
         <v>0.001533742331288344</v>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9030,27 +9231,32 @@
           <t>Americas Hotels Group</t>
         </is>
       </c>
-      <c r="C45" s="12" t="n">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="n">
         <v>636</v>
       </c>
-      <c r="D45" s="12" t="n">
+      <c r="E45" s="12" t="n">
         <v>597</v>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="F45" s="13" t="n">
+      <c r="G45" s="13" t="n">
         <v>0.9386792452830188</v>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="H45" s="13" t="n">
         <v>0.02987421383647799</v>
       </c>
-      <c r="H45" s="9" t="inlineStr">
+      <c r="I45" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -9065,27 +9271,32 @@
           <t>Sandos</t>
         </is>
       </c>
-      <c r="C46" s="12" t="n">
-        <v>489</v>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D46" s="12" t="n">
         <v>489</v>
       </c>
       <c r="E46" s="12" t="n">
+        <v>489</v>
+      </c>
+      <c r="F46" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F46" s="13" t="n">
+      <c r="G46" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="13" t="n">
+      <c r="H46" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -9100,27 +9311,32 @@
           <t>Pueblo Bonito</t>
         </is>
       </c>
-      <c r="C47" s="12" t="n">
-        <v>337</v>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D47" s="12" t="n">
         <v>337</v>
       </c>
       <c r="E47" s="12" t="n">
+        <v>337</v>
+      </c>
+      <c r="F47" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="F47" s="13" t="n">
+      <c r="G47" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="13" t="n">
+      <c r="H47" s="13" t="n">
         <v>0.03264094955489615</v>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -9135,27 +9351,32 @@
           <t>El Dorado San Andrés</t>
         </is>
       </c>
-      <c r="C48" s="12" t="n">
-        <v>308</v>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D48" s="12" t="n">
         <v>308</v>
       </c>
       <c r="E48" s="12" t="n">
+        <v>308</v>
+      </c>
+      <c r="F48" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F48" s="13" t="n">
+      <c r="G48" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="13" t="n">
+      <c r="H48" s="13" t="n">
         <v>0.01948051948051948</v>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="J48" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -9170,27 +9391,32 @@
           <t>EM Hotels</t>
         </is>
       </c>
-      <c r="C49" s="12" t="n">
-        <v>303</v>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
       </c>
       <c r="D49" s="12" t="n">
         <v>303</v>
       </c>
       <c r="E49" s="12" t="n">
+        <v>303</v>
+      </c>
+      <c r="F49" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F49" s="13" t="n">
+      <c r="G49" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G49" s="13" t="n">
+      <c r="H49" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -9205,27 +9431,32 @@
           <t>Villa Group</t>
         </is>
       </c>
-      <c r="C50" s="12" t="n">
-        <v>300</v>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D50" s="12" t="n">
         <v>300</v>
       </c>
       <c r="E50" s="12" t="n">
+        <v>300</v>
+      </c>
+      <c r="F50" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F50" s="13" t="n">
+      <c r="G50" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G50" s="13" t="n">
+      <c r="H50" s="13" t="n">
         <v>0.02</v>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -9240,27 +9471,32 @@
           <t>Hoteles Solar</t>
         </is>
       </c>
-      <c r="C51" s="12" t="n">
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="n">
         <v>289</v>
       </c>
-      <c r="D51" s="12" t="n">
+      <c r="E51" s="12" t="n">
         <v>288</v>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="F51" s="13" t="n">
+      <c r="G51" s="13" t="n">
         <v>0.9965397923875432</v>
       </c>
-      <c r="G51" s="13" t="n">
+      <c r="H51" s="13" t="n">
         <v>0.03806228373702422</v>
       </c>
-      <c r="H51" s="10" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -9275,27 +9511,32 @@
           <t>Faranda Hotels</t>
         </is>
       </c>
-      <c r="C52" s="12" t="n">
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="n">
         <v>269</v>
       </c>
-      <c r="D52" s="12" t="n">
+      <c r="E52" s="12" t="n">
         <v>268</v>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F52" s="13" t="n">
+      <c r="G52" s="13" t="n">
         <v>0.9962825278810409</v>
       </c>
-      <c r="G52" s="13" t="n">
+      <c r="H52" s="13" t="n">
         <v>0.003717472118959108</v>
       </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9310,27 +9551,32 @@
           <t>Dorado Plaza</t>
         </is>
       </c>
-      <c r="C53" s="12" t="n">
-        <v>246</v>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
       </c>
       <c r="D53" s="12" t="n">
         <v>246</v>
       </c>
       <c r="E53" s="12" t="n">
+        <v>246</v>
+      </c>
+      <c r="F53" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F53" s="13" t="n">
+      <c r="G53" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="13" t="n">
+      <c r="H53" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="10" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -9345,27 +9591,32 @@
           <t>Station Casinos</t>
         </is>
       </c>
-      <c r="C54" s="12" t="n">
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="n">
         <v>233</v>
-      </c>
-      <c r="D54" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="E54" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F54" s="13" t="n">
+      <c r="F54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G54" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="4" t="inlineStr">
+      <c r="H54" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -9380,27 +9631,32 @@
           <t>BH Hoteles</t>
         </is>
       </c>
-      <c r="C55" s="12" t="n">
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="n">
         <v>211</v>
       </c>
-      <c r="D55" s="12" t="n">
+      <c r="E55" s="12" t="n">
         <v>210</v>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="F55" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F55" s="13" t="n">
+      <c r="G55" s="13" t="n">
         <v>0.995260663507109</v>
       </c>
-      <c r="G55" s="13" t="n">
+      <c r="H55" s="13" t="n">
         <v>0.01895734597156398</v>
       </c>
-      <c r="H55" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -9448,7 +9704,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11292,7 +11548,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11791,7 +12047,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-19/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-19/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -3184,7 +3184,7 @@
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
@@ -3208,7 +3208,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -5383,7 +5383,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="37" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
@@ -5407,7 +5407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -7580,7 +7580,7 @@
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -7606,7 +7606,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -7628,7 +7628,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -9678,7 +9678,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
@@ -9704,7 +9704,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -11522,7 +11522,7 @@
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -11548,7 +11548,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -12023,7 +12023,7 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
@@ -12047,7 +12047,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
